--- a/artfynd/A 29103-2024 artfynd.xlsx
+++ b/artfynd/A 29103-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AY129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120726773</v>
+        <v>120726733</v>
       </c>
       <c r="B2" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548279</v>
+        <v>548648</v>
       </c>
       <c r="R2" t="n">
-        <v>6968056</v>
+        <v>6967981</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,53 +772,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120726828</v>
+        <v>129640379</v>
       </c>
       <c r="B3" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Täckelsjön, Jmt</t>
+          <t>Hucksjöåsen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548537</v>
+        <v>548468</v>
       </c>
       <c r="R3" t="n">
-        <v>6967988</v>
+        <v>6968143</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +841,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,49 +871,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120726885</v>
+        <v>120726797</v>
       </c>
       <c r="B4" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548642</v>
+        <v>548782</v>
       </c>
       <c r="R4" t="n">
-        <v>6967949</v>
+        <v>6967923</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +980,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120726751</v>
+        <v>120726799</v>
       </c>
       <c r="B5" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>1958</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1015,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548432</v>
+        <v>548707</v>
       </c>
       <c r="R5" t="n">
-        <v>6968007</v>
+        <v>6967953</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,37 +1077,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120726732</v>
+        <v>120726800</v>
       </c>
       <c r="B6" t="n">
-        <v>90183</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>256703</v>
+        <v>1958</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1112,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548668</v>
+        <v>548579</v>
       </c>
       <c r="R6" t="n">
-        <v>6967932</v>
+        <v>6967956</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,37 +1174,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120726852</v>
+        <v>120726801</v>
       </c>
       <c r="B7" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1209,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548486</v>
+        <v>548423</v>
       </c>
       <c r="R7" t="n">
-        <v>6968099</v>
+        <v>6967997</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,37 +1271,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120726744</v>
+        <v>120726802</v>
       </c>
       <c r="B8" t="n">
-        <v>91974</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2059</v>
+        <v>1958</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1306,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>548565</v>
+        <v>548414</v>
       </c>
       <c r="R8" t="n">
-        <v>6967968</v>
+        <v>6968000</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,15 +1368,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120726815</v>
+        <v>120726804</v>
       </c>
       <c r="B9" t="n">
-        <v>98059</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1379,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1958</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1403,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548300</v>
+        <v>548369</v>
       </c>
       <c r="R9" t="n">
-        <v>6968023</v>
+        <v>6967988</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,37 +1465,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120726820</v>
+        <v>120726805</v>
       </c>
       <c r="B10" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>548789</v>
+        <v>548527</v>
       </c>
       <c r="R10" t="n">
-        <v>6967879</v>
+        <v>6967961</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,37 +1562,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120726840</v>
+        <v>120726806</v>
       </c>
       <c r="B11" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>548405</v>
+        <v>548623</v>
       </c>
       <c r="R11" t="n">
-        <v>6967978</v>
+        <v>6967936</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,37 +1659,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120726779</v>
+        <v>120726807</v>
       </c>
       <c r="B12" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>1958</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1694,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>548557</v>
+        <v>548591</v>
       </c>
       <c r="R12" t="n">
-        <v>6967948</v>
+        <v>6968001</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,37 +1756,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120726835</v>
+        <v>120726808</v>
       </c>
       <c r="B13" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>1958</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1791,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>548364</v>
+        <v>548609</v>
       </c>
       <c r="R13" t="n">
-        <v>6968017</v>
+        <v>6967997</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,37 +1853,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120726776</v>
+        <v>120726809</v>
       </c>
       <c r="B14" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4361</v>
+        <v>1958</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1888,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>548334</v>
+        <v>548597</v>
       </c>
       <c r="R14" t="n">
-        <v>6967993</v>
+        <v>6967992</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,37 +1950,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120726898</v>
+        <v>120726811</v>
       </c>
       <c r="B15" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>1958</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +1985,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>548317</v>
+        <v>548632</v>
       </c>
       <c r="R15" t="n">
-        <v>6968018</v>
+        <v>6967933</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,15 +2047,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120726805</v>
+        <v>120726812</v>
       </c>
       <c r="B16" t="n">
-        <v>91431</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2143,10 +2082,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>548527</v>
+        <v>548660</v>
       </c>
       <c r="R16" t="n">
-        <v>6967961</v>
+        <v>6967939</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,37 +2144,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120726719</v>
+        <v>120726813</v>
       </c>
       <c r="B17" t="n">
-        <v>86233</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92692</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3690</v>
+        <v>1958</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Lammticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Albatrellus subrubescens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Murrill) Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2179,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>548381</v>
+        <v>548235</v>
       </c>
       <c r="R17" t="n">
-        <v>6968017</v>
+        <v>6968062</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,53 +2241,52 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120726833</v>
+        <v>129640381</v>
       </c>
       <c r="B18" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Täckelsjön, Jmt</t>
+          <t>Hucksjöåsen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>548394</v>
+        <v>548466</v>
       </c>
       <c r="R18" t="n">
-        <v>6968006</v>
+        <v>6968147</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2377,12 +2310,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-09-09</t>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2397,49 +2340,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Annica Berglind</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120726846</v>
+        <v>120726744</v>
       </c>
       <c r="B19" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2387,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>548573</v>
+        <v>548565</v>
       </c>
       <c r="R19" t="n">
-        <v>6967963</v>
+        <v>6967968</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,37 +2449,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120726859</v>
+        <v>120726745</v>
       </c>
       <c r="B20" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2613,37 +2546,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120726829</v>
+        <v>120726746</v>
       </c>
       <c r="B21" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2581,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>548468</v>
+        <v>548569</v>
       </c>
       <c r="R21" t="n">
-        <v>6967994</v>
+        <v>6968022</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,37 +2643,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120726728</v>
+        <v>120726749</v>
       </c>
       <c r="B22" t="n">
-        <v>90183</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>256703</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2678,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>548773</v>
+        <v>548710</v>
       </c>
       <c r="R22" t="n">
-        <v>6967926</v>
+        <v>6967978</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,15 +2740,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120726788</v>
+        <v>120726792</v>
       </c>
       <c r="B23" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2833,21 +2751,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>2079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2775,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>548636</v>
+        <v>548558</v>
       </c>
       <c r="R23" t="n">
-        <v>6967917</v>
+        <v>6968026</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,37 +2837,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120726831</v>
+        <v>120726718</v>
       </c>
       <c r="B24" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91831</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2959,10 +2872,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>548414</v>
+        <v>548466</v>
       </c>
       <c r="R24" t="n">
-        <v>6968003</v>
+        <v>6968005</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3021,37 +2934,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120726753</v>
+        <v>120726719</v>
       </c>
       <c r="B25" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4366</v>
+        <v>3690</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +2969,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>548269</v>
+        <v>548381</v>
       </c>
       <c r="R25" t="n">
-        <v>6968066</v>
+        <v>6968017</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3123,15 +3031,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120726724</v>
+        <v>120726720</v>
       </c>
       <c r="B26" t="n">
-        <v>57501</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3139,21 +3042,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>3690</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3066,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>548301</v>
+        <v>548656</v>
       </c>
       <c r="R26" t="n">
-        <v>6968082</v>
+        <v>6967989</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3225,37 +3128,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120726839</v>
+        <v>120726793</v>
       </c>
       <c r="B27" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>3690</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3163,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>548388</v>
+        <v>548665</v>
       </c>
       <c r="R27" t="n">
-        <v>6967988</v>
+        <v>6967977</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,15 +3225,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120726772</v>
+        <v>120726770</v>
       </c>
       <c r="B28" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3367,10 +3260,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>548340</v>
+        <v>548624</v>
       </c>
       <c r="R28" t="n">
-        <v>6968111</v>
+        <v>6967941</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3429,37 +3322,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120726850</v>
+        <v>120726771</v>
       </c>
       <c r="B29" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3469,10 +3357,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>548476</v>
+        <v>548408</v>
       </c>
       <c r="R29" t="n">
-        <v>6968017</v>
+        <v>6968005</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3531,37 +3419,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120726857</v>
+        <v>120726772</v>
       </c>
       <c r="B30" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3571,10 +3454,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>548546</v>
+        <v>548340</v>
       </c>
       <c r="R30" t="n">
-        <v>6968026</v>
+        <v>6968111</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3633,15 +3516,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120726718</v>
+        <v>120726773</v>
       </c>
       <c r="B31" t="n">
-        <v>90608</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3649,21 +3527,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3242</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3673,10 +3551,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>548466</v>
+        <v>548279</v>
       </c>
       <c r="R31" t="n">
-        <v>6968005</v>
+        <v>6968056</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,37 +3613,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120726763</v>
+        <v>120726774</v>
       </c>
       <c r="B32" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3775,10 +3648,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>548644</v>
+        <v>548300</v>
       </c>
       <c r="R32" t="n">
-        <v>6967969</v>
+        <v>6968023</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3837,37 +3710,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120726856</v>
+        <v>120726775</v>
       </c>
       <c r="B33" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3877,10 +3745,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>548552</v>
+        <v>548324</v>
       </c>
       <c r="R33" t="n">
-        <v>6968022</v>
+        <v>6968012</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,37 +3807,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120726877</v>
+        <v>120726776</v>
       </c>
       <c r="B34" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3979,10 +3842,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>548622</v>
+        <v>548334</v>
       </c>
       <c r="R34" t="n">
-        <v>6967983</v>
+        <v>6967993</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4041,37 +3904,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120726752</v>
+        <v>120726777</v>
       </c>
       <c r="B35" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4366</v>
+        <v>4361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4081,10 +3939,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>548306</v>
+        <v>548405</v>
       </c>
       <c r="R35" t="n">
-        <v>6968096</v>
+        <v>6967978</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,37 +4001,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120726809</v>
+        <v>120726778</v>
       </c>
       <c r="B36" t="n">
-        <v>91431</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1958</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4183,10 +4036,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>548597</v>
+        <v>548548</v>
       </c>
       <c r="R36" t="n">
-        <v>6967992</v>
+        <v>6967945</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4245,37 +4098,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120726848</v>
+        <v>120726779</v>
       </c>
       <c r="B37" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4285,10 +4133,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>548476</v>
+        <v>548557</v>
       </c>
       <c r="R37" t="n">
-        <v>6967982</v>
+        <v>6967948</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4347,37 +4195,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120726883</v>
+        <v>120726780</v>
       </c>
       <c r="B38" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4387,10 +4230,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>548644</v>
+        <v>548546</v>
       </c>
       <c r="R38" t="n">
-        <v>6967969</v>
+        <v>6968026</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4449,15 +4292,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120726791</v>
+        <v>120726781</v>
       </c>
       <c r="B39" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4489,10 +4327,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>548443</v>
+        <v>548560</v>
       </c>
       <c r="R39" t="n">
-        <v>6967969</v>
+        <v>6967999</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4551,37 +4389,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120726853</v>
+        <v>120726783</v>
       </c>
       <c r="B40" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4591,10 +4424,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>548501</v>
+        <v>548595</v>
       </c>
       <c r="R40" t="n">
-        <v>6968090</v>
+        <v>6968002</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4653,15 +4486,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120726771</v>
+        <v>120726784</v>
       </c>
       <c r="B41" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4693,10 +4521,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>548408</v>
+        <v>548596</v>
       </c>
       <c r="R41" t="n">
-        <v>6968005</v>
+        <v>6967959</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4755,37 +4583,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120726822</v>
+        <v>120726785</v>
       </c>
       <c r="B42" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4795,10 +4618,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>548755</v>
+        <v>548645</v>
       </c>
       <c r="R42" t="n">
-        <v>6967933</v>
+        <v>6967985</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4857,15 +4680,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120726738</v>
+        <v>120726786</v>
       </c>
       <c r="B43" t="n">
-        <v>91986</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4873,21 +4691,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4897,10 +4715,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>548646</v>
+        <v>548670</v>
       </c>
       <c r="R43" t="n">
-        <v>6967943</v>
+        <v>6967975</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4959,37 +4777,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120726841</v>
+        <v>120726787</v>
       </c>
       <c r="B44" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4999,10 +4812,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>548429</v>
+        <v>548689</v>
       </c>
       <c r="R44" t="n">
-        <v>6967966</v>
+        <v>6967968</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5061,37 +4874,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120726845</v>
+        <v>120726788</v>
       </c>
       <c r="B45" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5101,10 +4909,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>548542</v>
+        <v>548636</v>
       </c>
       <c r="R45" t="n">
-        <v>6967963</v>
+        <v>6967917</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5163,37 +4971,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120726843</v>
+        <v>120726790</v>
       </c>
       <c r="B46" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5203,10 +5006,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>548456</v>
+        <v>548532</v>
       </c>
       <c r="R46" t="n">
-        <v>6967962</v>
+        <v>6968096</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5265,37 +5068,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120726832</v>
+        <v>120726791</v>
       </c>
       <c r="B47" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5305,10 +5103,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>548403</v>
+        <v>548443</v>
       </c>
       <c r="R47" t="n">
-        <v>6968007</v>
+        <v>6967969</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5367,37 +5165,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120726801</v>
+        <v>120726896</v>
       </c>
       <c r="B48" t="n">
-        <v>91431</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1958</v>
+        <v>4362</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5407,10 +5200,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>548423</v>
+        <v>548697</v>
       </c>
       <c r="R48" t="n">
-        <v>6967997</v>
+        <v>6967942</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5469,15 +5262,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120726745</v>
+        <v>120726897</v>
       </c>
       <c r="B49" t="n">
-        <v>91974</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5485,21 +5273,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5509,10 +5297,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>548548</v>
+        <v>548486</v>
       </c>
       <c r="R49" t="n">
-        <v>6967983</v>
+        <v>6967990</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5571,15 +5359,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120726784</v>
+        <v>120726898</v>
       </c>
       <c r="B50" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5587,21 +5370,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5611,10 +5394,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>548596</v>
+        <v>548317</v>
       </c>
       <c r="R50" t="n">
-        <v>6967959</v>
+        <v>6968018</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5673,37 +5456,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120726892</v>
+        <v>120726899</v>
       </c>
       <c r="B51" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5713,10 +5491,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>548668</v>
+        <v>548329</v>
       </c>
       <c r="R51" t="n">
-        <v>6967930</v>
+        <v>6968005</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5775,15 +5553,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120726725</v>
+        <v>120726820</v>
       </c>
       <c r="B52" t="n">
-        <v>57501</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5791,21 +5564,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5815,10 +5588,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>548658</v>
+        <v>548789</v>
       </c>
       <c r="R52" t="n">
-        <v>6967943</v>
+        <v>6967879</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5877,37 +5650,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120726804</v>
+        <v>120726821</v>
       </c>
       <c r="B53" t="n">
-        <v>91431</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5917,10 +5685,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>548369</v>
+        <v>548785</v>
       </c>
       <c r="R53" t="n">
-        <v>6967988</v>
+        <v>6967908</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5979,15 +5747,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120726897</v>
+        <v>120726822</v>
       </c>
       <c r="B54" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5995,21 +5758,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6019,10 +5782,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>548486</v>
+        <v>548755</v>
       </c>
       <c r="R54" t="n">
-        <v>6967990</v>
+        <v>6967933</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6081,19 +5844,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120726855</v>
+        <v>120726823</v>
       </c>
       <c r="B55" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6121,10 +5879,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>548490</v>
+        <v>548733</v>
       </c>
       <c r="R55" t="n">
-        <v>6968056</v>
+        <v>6967928</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6183,37 +5941,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120726811</v>
+        <v>120726824</v>
       </c>
       <c r="B56" t="n">
-        <v>91431</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6223,10 +5976,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>548632</v>
+        <v>548727</v>
       </c>
       <c r="R56" t="n">
-        <v>6967933</v>
+        <v>6967943</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6285,37 +6038,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120726806</v>
+        <v>120726825</v>
       </c>
       <c r="B57" t="n">
-        <v>91431</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6325,10 +6073,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>548623</v>
+        <v>548722</v>
       </c>
       <c r="R57" t="n">
-        <v>6967936</v>
+        <v>6967952</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6387,15 +6135,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120726727</v>
+        <v>120726826</v>
       </c>
       <c r="B58" t="n">
-        <v>90702</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6403,21 +6146,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6427,10 +6170,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>548534</v>
+        <v>548714</v>
       </c>
       <c r="R58" t="n">
-        <v>6968011</v>
+        <v>6967961</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6489,15 +6232,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120726780</v>
+        <v>120726827</v>
       </c>
       <c r="B59" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6505,21 +6243,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6529,10 +6267,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>548546</v>
+        <v>548551</v>
       </c>
       <c r="R59" t="n">
-        <v>6968026</v>
+        <v>6967977</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6591,15 +6329,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120726775</v>
+        <v>120726828</v>
       </c>
       <c r="B60" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6607,21 +6340,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6631,10 +6364,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>548324</v>
+        <v>548537</v>
       </c>
       <c r="R60" t="n">
-        <v>6968012</v>
+        <v>6967988</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6693,37 +6426,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120726730</v>
+        <v>120726829</v>
       </c>
       <c r="B61" t="n">
-        <v>90183</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6733,10 +6461,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>548592</v>
+        <v>548468</v>
       </c>
       <c r="R61" t="n">
-        <v>6967992</v>
+        <v>6967994</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6795,37 +6523,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120726812</v>
+        <v>120726830</v>
       </c>
       <c r="B62" t="n">
-        <v>91431</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6835,10 +6558,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>548660</v>
+        <v>548438</v>
       </c>
       <c r="R62" t="n">
-        <v>6967939</v>
+        <v>6967992</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6897,15 +6620,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120726770</v>
+        <v>120726831</v>
       </c>
       <c r="B63" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6913,21 +6631,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6937,10 +6655,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>548624</v>
+        <v>548414</v>
       </c>
       <c r="R63" t="n">
-        <v>6967941</v>
+        <v>6968003</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6999,15 +6717,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120726774</v>
+        <v>120726832</v>
       </c>
       <c r="B64" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7015,21 +6728,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7039,10 +6752,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>548300</v>
+        <v>548403</v>
       </c>
       <c r="R64" t="n">
-        <v>6968023</v>
+        <v>6968007</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7101,19 +6814,14 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120726837</v>
+        <v>120726833</v>
       </c>
       <c r="B65" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -7141,10 +6849,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>548329</v>
+        <v>548394</v>
       </c>
       <c r="R65" t="n">
-        <v>6968120</v>
+        <v>6968006</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7203,15 +6911,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120726899</v>
+        <v>120726835</v>
       </c>
       <c r="B66" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7219,21 +6922,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7243,10 +6946,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>548329</v>
+        <v>548364</v>
       </c>
       <c r="R66" t="n">
-        <v>6968005</v>
+        <v>6968017</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7305,19 +7008,14 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120726838</v>
+        <v>120726836</v>
       </c>
       <c r="B67" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -7345,10 +7043,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>548270</v>
+        <v>548322</v>
       </c>
       <c r="R67" t="n">
-        <v>6968052</v>
+        <v>6968054</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7407,19 +7105,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120726827</v>
+        <v>120726837</v>
       </c>
       <c r="B68" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -7447,10 +7140,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>548551</v>
+        <v>548329</v>
       </c>
       <c r="R68" t="n">
-        <v>6967977</v>
+        <v>6968120</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7509,37 +7202,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120726755</v>
+        <v>120726838</v>
       </c>
       <c r="B69" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7549,10 +7237,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>548584</v>
+        <v>548270</v>
       </c>
       <c r="R69" t="n">
-        <v>6967934</v>
+        <v>6968052</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7611,19 +7299,14 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120726849</v>
+        <v>120726839</v>
       </c>
       <c r="B70" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -7651,10 +7334,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>548475</v>
+        <v>548388</v>
       </c>
       <c r="R70" t="n">
-        <v>6967995</v>
+        <v>6967988</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7713,19 +7396,14 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120726851</v>
+        <v>120726840</v>
       </c>
       <c r="B71" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -7753,10 +7431,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>548473</v>
+        <v>548405</v>
       </c>
       <c r="R71" t="n">
-        <v>6968050</v>
+        <v>6967978</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7815,19 +7493,14 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120726842</v>
+        <v>120726841</v>
       </c>
       <c r="B72" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -7855,10 +7528,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>548447</v>
+        <v>548429</v>
       </c>
       <c r="R72" t="n">
-        <v>6967977</v>
+        <v>6967966</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7917,37 +7590,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120726729</v>
+        <v>120726842</v>
       </c>
       <c r="B73" t="n">
-        <v>90183</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>256703</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7957,10 +7625,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>548433</v>
+        <v>548447</v>
       </c>
       <c r="R73" t="n">
-        <v>6967997</v>
+        <v>6967977</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8019,37 +7687,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120726797</v>
+        <v>120726843</v>
       </c>
       <c r="B74" t="n">
-        <v>91431</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8059,10 +7722,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>548782</v>
+        <v>548456</v>
       </c>
       <c r="R74" t="n">
-        <v>6967923</v>
+        <v>6967962</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8121,37 +7784,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120726802</v>
+        <v>120726844</v>
       </c>
       <c r="B75" t="n">
-        <v>91431</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8161,10 +7819,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>548414</v>
+        <v>548520</v>
       </c>
       <c r="R75" t="n">
-        <v>6968000</v>
+        <v>6967967</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8223,19 +7881,14 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120726858</v>
+        <v>120726845</v>
       </c>
       <c r="B76" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -8263,10 +7916,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>548537</v>
+        <v>548542</v>
       </c>
       <c r="R76" t="n">
-        <v>6968021</v>
+        <v>6967963</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8325,19 +7978,14 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120726895</v>
+        <v>120726846</v>
       </c>
       <c r="B77" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -8365,10 +8013,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>548619</v>
+        <v>548573</v>
       </c>
       <c r="R77" t="n">
-        <v>6967958</v>
+        <v>6967963</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8427,19 +8075,14 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120726821</v>
+        <v>120726847</v>
       </c>
       <c r="B78" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -8467,10 +8110,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>548785</v>
+        <v>548538</v>
       </c>
       <c r="R78" t="n">
-        <v>6967908</v>
+        <v>6967986</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8529,37 +8172,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120726754</v>
+        <v>120726848</v>
       </c>
       <c r="B79" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8569,10 +8207,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>548340</v>
+        <v>548476</v>
       </c>
       <c r="R79" t="n">
-        <v>6968000</v>
+        <v>6967982</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8631,19 +8269,14 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120726876</v>
+        <v>120726849</v>
       </c>
       <c r="B80" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -8671,10 +8304,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>548599</v>
+        <v>548475</v>
       </c>
       <c r="R80" t="n">
-        <v>6967963</v>
+        <v>6967995</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8733,37 +8366,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120726750</v>
+        <v>120726850</v>
       </c>
       <c r="B81" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8773,10 +8401,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>548537</v>
+        <v>548476</v>
       </c>
       <c r="R81" t="n">
-        <v>6967985</v>
+        <v>6968017</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8835,15 +8463,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120726778</v>
+        <v>120726851</v>
       </c>
       <c r="B82" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8851,21 +8474,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8875,10 +8498,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>548548</v>
+        <v>548473</v>
       </c>
       <c r="R82" t="n">
-        <v>6967945</v>
+        <v>6968050</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8937,37 +8560,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120726800</v>
+        <v>120726852</v>
       </c>
       <c r="B83" t="n">
-        <v>91431</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1958</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lammticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Albatrellus subrubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Murrill) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8977,10 +8595,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>548579</v>
+        <v>548486</v>
       </c>
       <c r="R83" t="n">
-        <v>6967956</v>
+        <v>6968099</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9039,37 +8657,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120726743</v>
+        <v>120726853</v>
       </c>
       <c r="B84" t="n">
-        <v>91942</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9079,10 +8692,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>548660</v>
+        <v>548501</v>
       </c>
       <c r="R84" t="n">
-        <v>6967930</v>
+        <v>6968090</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9141,37 +8754,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120726814</v>
+        <v>120726855</v>
       </c>
       <c r="B85" t="n">
-        <v>98059</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9181,10 +8789,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>548744</v>
+        <v>548490</v>
       </c>
       <c r="R85" t="n">
-        <v>6967890</v>
+        <v>6968056</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9243,19 +8851,14 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120726884</v>
+        <v>120726856</v>
       </c>
       <c r="B86" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -9283,10 +8886,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>548643</v>
+        <v>548552</v>
       </c>
       <c r="R86" t="n">
-        <v>6967952</v>
+        <v>6968022</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9345,19 +8948,14 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120726836</v>
+        <v>120726857</v>
       </c>
       <c r="B87" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -9385,10 +8983,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>548322</v>
+        <v>548546</v>
       </c>
       <c r="R87" t="n">
-        <v>6968054</v>
+        <v>6968026</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9447,15 +9045,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120726792</v>
+        <v>120726858</v>
       </c>
       <c r="B88" t="n">
-        <v>92155</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9463,21 +9056,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2079</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9487,10 +9080,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>548558</v>
+        <v>548537</v>
       </c>
       <c r="R88" t="n">
-        <v>6968026</v>
+        <v>6968021</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9549,19 +9142,14 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120726875</v>
+        <v>120726859</v>
       </c>
       <c r="B89" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
@@ -9589,10 +9177,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>548585</v>
+        <v>548548</v>
       </c>
       <c r="R89" t="n">
-        <v>6967987</v>
+        <v>6967983</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9651,15 +9239,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120726777</v>
+        <v>120726860</v>
       </c>
       <c r="B90" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9667,21 +9250,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9691,10 +9274,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>548405</v>
+        <v>548592</v>
       </c>
       <c r="R90" t="n">
-        <v>6967978</v>
+        <v>6968015</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9753,19 +9336,14 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120726830</v>
+        <v>120726873</v>
       </c>
       <c r="B91" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -9793,10 +9371,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>548438</v>
+        <v>548610</v>
       </c>
       <c r="R91" t="n">
-        <v>6967992</v>
+        <v>6968010</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9855,19 +9433,14 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120726844</v>
+        <v>120726874</v>
       </c>
       <c r="B92" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -9895,10 +9468,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>548520</v>
+        <v>548610</v>
       </c>
       <c r="R92" t="n">
-        <v>6967967</v>
+        <v>6968007</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9957,19 +9530,14 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120726847</v>
+        <v>120726875</v>
       </c>
       <c r="B93" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
@@ -9997,10 +9565,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>548538</v>
+        <v>548585</v>
       </c>
       <c r="R93" t="n">
-        <v>6967986</v>
+        <v>6967987</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10059,37 +9627,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120726816</v>
+        <v>120726876</v>
       </c>
       <c r="B94" t="n">
-        <v>98059</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10099,10 +9662,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>548560</v>
+        <v>548599</v>
       </c>
       <c r="R94" t="n">
-        <v>6967950</v>
+        <v>6967963</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10158,6 +9721,3415 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>120726877</v>
+      </c>
+      <c r="B95" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>548622</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6967983</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>120726878</v>
+      </c>
+      <c r="B96" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>548638</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6968000</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>120726882</v>
+      </c>
+      <c r="B97" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>548650</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6967982</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>120726883</v>
+      </c>
+      <c r="B98" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>548644</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6967969</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>120726884</v>
+      </c>
+      <c r="B99" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>548643</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6967952</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>120726885</v>
+      </c>
+      <c r="B100" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>548642</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6967949</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>120726887</v>
+      </c>
+      <c r="B101" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>548667</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6967959</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>120726888</v>
+      </c>
+      <c r="B102" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>548670</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6967976</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>120726889</v>
+      </c>
+      <c r="B103" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>548680</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6967977</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>120726891</v>
+      </c>
+      <c r="B104" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>548689</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6967968</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>120726892</v>
+      </c>
+      <c r="B105" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>548668</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6967930</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>120726893</v>
+      </c>
+      <c r="B106" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>548700</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6967990</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>120726895</v>
+      </c>
+      <c r="B107" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>548619</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6967958</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>129640380</v>
+      </c>
+      <c r="B108" t="n">
+        <v>93201</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Hucksjöåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>548464</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6968145</v>
+      </c>
+      <c r="S108" t="n">
+        <v>5</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-11-05</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>12:10</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Annica Berglind</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>120726750</v>
+      </c>
+      <c r="B109" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>548537</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6967985</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>120726751</v>
+      </c>
+      <c r="B110" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>548432</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6968007</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>120726752</v>
+      </c>
+      <c r="B111" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>548306</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6968096</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>120726753</v>
+      </c>
+      <c r="B112" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>548269</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6968066</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>120726754</v>
+      </c>
+      <c r="B113" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>548340</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6968000</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>120726755</v>
+      </c>
+      <c r="B114" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>548584</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6967934</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>120726757</v>
+      </c>
+      <c r="B115" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>548571</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6968019</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>120726763</v>
+      </c>
+      <c r="B116" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>548644</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6967969</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>120726765</v>
+      </c>
+      <c r="B117" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>548698</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6967974</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>120726767</v>
+      </c>
+      <c r="B118" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>548678</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6967956</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>120726727</v>
+      </c>
+      <c r="B119" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>548534</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6968011</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>120726743</v>
+      </c>
+      <c r="B120" t="n">
+        <v>93181</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>548660</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6967930</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120726724</v>
+      </c>
+      <c r="B121" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>548301</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6968082</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>120726725</v>
+      </c>
+      <c r="B122" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>548658</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6967943</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>120726814</v>
+      </c>
+      <c r="B123" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>548744</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6967890</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>120726815</v>
+      </c>
+      <c r="B124" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>548300</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6968023</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>120726816</v>
+      </c>
+      <c r="B125" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>548560</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6967950</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>120726728</v>
+      </c>
+      <c r="B126" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>548773</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6967926</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>120726729</v>
+      </c>
+      <c r="B127" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>548433</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6967997</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>120726730</v>
+      </c>
+      <c r="B128" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>548592</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6967992</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>120726732</v>
+      </c>
+      <c r="B129" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Täckelsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>548668</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6967932</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29103-2024 artfynd.xlsx
+++ b/artfynd/A 29103-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY129"/>
+  <dimension ref="A1:AZ129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726733</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129640379</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726797</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726799</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726800</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726801</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1365,6 +1400,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726802</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1462,6 +1502,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726804</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1559,6 +1604,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726805</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1656,6 +1706,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726806</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1753,6 +1808,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726807</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1850,6 +1910,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726808</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1947,6 +2012,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726809</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2044,6 +2114,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726811</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2141,6 +2216,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726812</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2238,6 +2318,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726813</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2349,6 +2434,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129640381</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2446,6 +2536,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726744</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2543,6 +2638,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726745</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2640,6 +2740,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726746</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2737,6 +2842,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726749</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2834,6 +2944,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726792</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2931,6 +3046,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726718</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3028,6 +3148,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726719</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3125,6 +3250,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726720</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3222,6 +3352,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726793</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3319,6 +3454,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726770</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3416,6 +3556,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726771</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3513,6 +3658,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726772</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3610,6 +3760,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726773</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3707,6 +3862,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726774</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3804,6 +3964,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726775</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3901,6 +4066,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726776</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3998,6 +4168,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726777</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4095,6 +4270,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726778</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4192,6 +4372,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726779</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4289,6 +4474,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726780</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4386,6 +4576,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726781</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4483,6 +4678,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726783</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4580,6 +4780,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726784</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4677,6 +4882,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726785</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4774,6 +4984,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726786</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4871,6 +5086,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726787</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4968,6 +5188,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726788</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5065,6 +5290,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726790</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5162,6 +5392,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726791</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5259,6 +5494,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726896</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5356,6 +5596,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726897</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5453,6 +5698,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726898</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5550,6 +5800,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726899</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5647,6 +5902,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726820</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5744,6 +6004,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726821</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5841,6 +6106,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726822</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5938,6 +6208,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726823</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6035,6 +6310,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726824</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6132,6 +6412,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726825</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6229,6 +6514,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726826</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6326,6 +6616,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726827</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6423,6 +6718,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726828</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6520,6 +6820,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726829</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6617,6 +6922,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726830</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6714,6 +7024,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726831</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6811,6 +7126,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726832</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6908,6 +7228,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726833</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7005,6 +7330,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726835</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7102,6 +7432,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726836</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7199,6 +7534,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726837</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7296,6 +7636,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726838</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7393,6 +7738,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726839</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7490,6 +7840,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726840</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7587,6 +7942,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726841</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7684,6 +8044,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726842</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7781,6 +8146,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726843</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7878,6 +8248,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726844</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7975,6 +8350,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726845</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8072,6 +8452,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726846</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8169,6 +8554,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726847</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8266,6 +8656,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726848</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8363,6 +8758,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726849</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8460,6 +8860,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726850</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8557,6 +8962,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726851</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8654,6 +9064,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726852</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8751,6 +9166,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726853</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8848,6 +9268,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726855</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8945,6 +9370,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726856</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9042,6 +9472,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726857</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9139,6 +9574,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726858</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9236,6 +9676,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726859</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9333,6 +9778,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726860</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9430,6 +9880,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726873</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9527,6 +9982,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726874</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9624,6 +10084,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726875</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9721,6 +10186,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726876</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9818,6 +10288,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726877</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9915,6 +10390,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726878</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10012,6 +10492,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726882</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10109,6 +10594,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726883</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10206,6 +10696,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726884</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10303,6 +10798,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726885</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10400,6 +10900,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726887</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10497,6 +11002,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726888</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10594,6 +11104,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726889</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10691,6 +11206,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726891</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10788,6 +11308,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726892</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -10885,6 +11410,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726893</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -10982,6 +11512,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726895</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11093,6 +11628,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129640380</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11190,6 +11730,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726750</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11287,6 +11832,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726751</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11384,6 +11934,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726752</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11481,6 +12036,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726753</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11578,6 +12138,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726754</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11675,6 +12240,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726755</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11772,6 +12342,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726757</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -11869,6 +12444,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726763</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -11966,6 +12546,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726765</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12063,6 +12648,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726767</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12160,6 +12750,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726727</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12257,6 +12852,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726743</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12354,6 +12954,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726724</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12451,6 +13056,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726725</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12548,6 +13158,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726814</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12645,6 +13260,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726815</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12742,6 +13362,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726816</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -12839,6 +13464,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726728</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -12936,6 +13566,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726729</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13033,6 +13668,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726730</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13130,8 +13770,143 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120726732</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>